--- a/healthcare_forms/019_post_traumatic_prison_disorder_survey_template--healthcare_forms.xlsx
+++ b/healthcare_forms/019_post_traumatic_prison_disorder_survey_template--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="39" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,10 +525,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Post Traumatic Prison Disorder Survey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Introduction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please take a few minutes to answer the following questions about your experiences with post-traumatic stress disorder.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>yes</t>
@@ -543,87 +547,103 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>introduction_subsection_1</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>introduction Subsection 1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your name for this survey.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>duration_of_symptoms</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Duration of Symptoms</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>How long have you been experiencing symptoms of post-traumatic stress disorder?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>symptoms_subsection_1</t>
+          <t>trauma_history</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>symptoms Subsection 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Trauma History</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Do you have a history of trauma?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>introduction_subsection_2</t>
+          <t>type_of_trauma</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>introduction Subsection 2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Type of Trauma</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What type of trauma have you experienced?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +655,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trauma_history</t>
+          <t>severity_of_symptoms</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trauma History</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Severity of Symptoms</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>How severe are your symptoms of post-traumatic stress disorder?</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,43 +677,51 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>trauma_history_subsection_1</t>
+          <t>symptoms_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>trauma History Subsection 1</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Symptoms</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>What are your symptoms of post-traumatic stress disorder?</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>trauma_history_subsection_2</t>
+          <t>symptoms_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>trauma History Subsection 2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Symptoms while Incarcerated</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Have you experienced any of the following symptoms while incarcerated?</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -704,18 +736,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>duration_incarceration</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Introduction</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Duration of Incarceration</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>How long have you been experiencing symptoms of post-traumatic stress disorder while incarcerated?</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +763,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>symptoms_subsection</t>
+          <t>symptoms_incarcerated_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Symptoms Subsection</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Symptoms Incarcerated 1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>What are your symptoms of post-traumatic stress disorder while incarcerated?</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,18 +790,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>trauma_subsection_1</t>
+          <t>severity_incarcerated</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Trauma Subsection 1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Severity of Symptoms while Incarcerated</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>How severe are your symptoms of post-traumatic stress disorder while incarcerated?</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,315 +817,101 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>trauma_subsection_2</t>
+          <t>stressors</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trauma Subsection 2</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Stressors</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>What has made you feel more anxious or stressed while incarcerated?</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trauma_subsection_3</t>
+          <t>trauma_history_incarcerated</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Trauma Subsection 3</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Trauma History while Incarcerated</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Have you experienced trauma while incarcerated?</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>introduction_subsection</t>
+          <t>comfort_disclosure</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Introduction Subsection</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Comfort with Disclosure</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Do you feel comfortable disclosing the following information?</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>symptoms_subsection_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Symptoms Subsection 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Is there anything else you would like to share or add to this survey?</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>introduction_subsection_3</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>introduction Subsection 3</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>trauma_subsection_4</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Trauma Subsection 4</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>introduction_subsection_4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>introduction Subsection 4</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>symptoms</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Symptoms</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>trauma</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Trauma</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>symptoms_subsection_3</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Symptoms Subsection 3</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>trauma_subsection_1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Trauma Subsection 1</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>introduction_subsection_5</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>introduction Subsection 5</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>trauma_subsection_2</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Trauma Subsection 2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>symptoms_subsection_4</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Symptoms Subsection 4</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +928,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,204 +956,340 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>trauma_history_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>item1</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>trauma_history_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>item2</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>type_of_trauma_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>physical_abuse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>item3</t>
+          <t>Physical Abuse</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>symptoms_subsection_choices</t>
+          <t>type_of_trauma_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>item4</t>
+          <t>emotional_abuse</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>item4</t>
+          <t>Emotional Abuse</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>symptoms_subsection_choices</t>
+          <t>type_of_trauma_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>item5</t>
+          <t>neglect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>item5</t>
+          <t>Neglect</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>symptoms_subsection_choices</t>
+          <t>type_of_trauma_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>item6</t>
+          <t>sexual_assault</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>item6</t>
+          <t>Sexual Assault</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>symptoms_subsection_2_choices</t>
+          <t>type_of_trauma_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>item7</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>item7</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>symptoms_subsection_2_choices</t>
+          <t>symptoms_1_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>item8</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>item8</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>symptoms_subsection_2_choices</t>
+          <t>symptoms_1_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>item9</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>item9</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>symptoms_subsection_3_choices</t>
+          <t>symptoms_1_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>item10</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>item10</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>symptoms_subsection_3_choices</t>
+          <t>symptoms_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>item11</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>item11</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>symptoms_subsection_3_choices</t>
+          <t>symptoms_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>item12</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>item12</t>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>symptoms_2_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>symptoms_incarcerated_1_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>symptoms_incarcerated_1_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>symptoms_incarcerated_1_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>trauma_history_incarcerated_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>trauma_history_incarcerated_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>comfort_disclosure_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>comfort_disclosure_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
